--- a/important_mails_2026-09-11.xlsx
+++ b/important_mails_2026-09-11.xlsx
@@ -2287,7 +2287,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2302,121 +2302,21 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Fri, 4 Sep 2026 20:46:54 +0000</t>
+          <t>Thu, 10 Sep 2026 03:39:41 +0000</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>"Comunicados de Amazon Seller Central (no responder)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Submit product safety documentation to reactivate listings</t>
+          <t>[Amazon.es] Hemos suprimido uno o varios de tus listings de las búsquedas en la web de Amazon</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 4 Sep 2026 20:32:31 +0000</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listing?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
--
- If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subj</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 10 Sep 2026 03:39:41 +0000</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>"Comunicados de Amazon Seller Central (no responder)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>[Amazon.es] Hemos suprimido uno o varios de tus listings de las búsquedas en la web de Amazon</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 [Amazon.es] Hemos suprimido uno o varios de tus listings de las búsquedas en la web de Amazon
@@ -2432,39 +2332,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 16:45:36 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Transparency No Reply &lt;noreply-transparency@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>OPR 体验优化——无需再手动追踪货件  /  Improvement to Your OPR Experience — No More Manual Shipment Tracking</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>尊敬的 Crifeton 团队：
 我们很高兴地通知您，OPR（Operational Performance Review运营表现评估）流程迎来一项优化，这将使开启 OPR 变得更加简单，并且您无需再手动追踪货件。
@@ -2488,39 +2388,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 16:45:33 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Transparency No Reply &lt;noreply-transparency@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>OPR 体验优化——无需再手动追踪货件  /  Improvement to Your OPR Experience — No More Manual Shipment Tracking</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>尊敬的 Crifeton 团队：
 我们很高兴地通知您，OPR（Operational Performance Review运营表现评估）流程迎来一项优化，这将使开启 OPR 变得更加简单，并且您无需再手动追踪货件。
@@ -2544,39 +2444,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 14:40:23 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 8/2026</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 8/2026
  96
@@ -2598,39 +2498,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 22:05:50 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Envía la documentación de seguridad del producto para evitar la desactivación de los listados</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai MX:
@@ -2647,39 +2547,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 16:05:13 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Actualiza los precios de venta recomendados a más tardar el 9 de septiembre de 2026</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
  Las nuevas reglas para validar los precios de referencia entran en vigor el 9 de septiembre de 2026.
@@ -2693,39 +2593,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 09:38:25 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Ottieni la tua garanzia IVA in Italia €2.350 rimborso fino a 31 dicembre</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -2741,39 +2641,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 05:09:23 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 8/2026</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 8/2026
  96
@@ -2791,39 +2691,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 05:02:45 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Verkäufer for 8/2026</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Verkäufer for 8/2026
  96
@@ -2847,40 +2747,40 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 04:49:12 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Credit Note for
  8/2026</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Credit Note for 8/2026
  96
@@ -2898,39 +2798,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 04:40:19 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 8/2026</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 8/2026
  96
@@ -2957,39 +2857,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 04:36:05 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 8/2026</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 8/2026
  96
@@ -3016,39 +2916,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 04:29:13 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 8/2026</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 8/2026
  96
@@ -3075,39 +2975,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 04:28:07 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 8/2026</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 8/2026
  96
@@ -3125,39 +3025,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 04:27:11 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Verkäufer for 8/2026</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Verkäufer for 8/2026
  96
@@ -3181,39 +3081,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 04:09:19 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 8/2026</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 8/2026
  96
@@ -3240,39 +3140,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 03:03:01 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Versand durch Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Versand durch Amazon for 8/2026
  96
@@ -3295,39 +3195,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 02:03:22 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Verkoper for 8/2026</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Verkoper for 8/2026
  96
@@ -3351,39 +3251,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 01:34:58 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 8/2026
  96
@@ -3410,39 +3310,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 01:08:53 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 8/2026</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 8/2026
  96
@@ -3460,39 +3360,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 01:06:25 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 8/2026
  96
@@ -3517,39 +3417,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 01:00:11 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 8/2026</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 8/2026
  96
@@ -3567,39 +3467,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 00:39:22 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 8/2026
  96
@@ -3623,39 +3523,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 23:59:03 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 8/2026
  96
@@ -3674,39 +3574,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 23:56:53 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 8/2026
  96
@@ -3733,39 +3633,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 23:48:47 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 8/2026
  96
@@ -3792,39 +3692,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 23:41:01 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 8/2026
  96
@@ -3849,39 +3749,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 23:09:33 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 8/2026</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 8/2026
  96
@@ -3906,39 +3806,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 22:41:45 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 8/2026</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 8/2026
  96
@@ -3965,39 +3865,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 22:38:15 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 8/2026
  96
@@ -4024,39 +3924,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 22:37:39 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 8/2026
  96
@@ -4080,39 +3980,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 22:25:15 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 8/2026
  96
@@ -4139,39 +4039,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 22:25:11 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 8/2026
  96
@@ -4196,39 +4096,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 22:18:55 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 8/2026
  96
@@ -4253,39 +4153,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 22:18:08 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Verkoper for 8/2026</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Verkoper for 8/2026
  96
@@ -4309,39 +4209,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 20:59:59 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Verkoper for 8/2026</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Verkoper for 8/2026
  96
@@ -4361,39 +4261,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 20:39:31 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -4409,39 +4309,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 20:29:23 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 8/2026
  96
@@ -4460,39 +4360,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 20:15:08 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 8/2026
  96
@@ -4511,39 +4411,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 19:50:44 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Sprzedawcy for 8/2026</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.pl Faktura Sprzedawcy for 8/2026
  96
@@ -4568,39 +4468,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 19:45:42 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 8/2026
  96
@@ -4627,39 +4527,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 19:11:44 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Selbstfakturierung AGL for 8/2026</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Selbstfakturierung AGL for 8/2026
  96
@@ -4684,39 +4584,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 19:06:41 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 8/2026</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 8/2026
  96
@@ -4741,39 +4641,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 18:35:49 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 8/2026
  96
@@ -4798,40 +4698,40 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 18:10:01 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -4849,39 +4749,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 18:08:44 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -4898,39 +4798,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 18:06:29 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -4948,39 +4848,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:50:58 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Realizacja przez Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Realizacja przez Amazon for 8/2026
  96
@@ -5004,39 +4904,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:16:06 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 8/2026</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 8/2026
  96
@@ -5063,39 +4963,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:08:49 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -5113,40 +5013,40 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:06:12 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -5164,39 +5064,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:05:11 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Säljare for 8/2026</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Säljare for 8/2026
  96
@@ -5223,39 +5123,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 16:47:02 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 8/2026</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 8/2026
  96
@@ -5273,39 +5173,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 15:12:47 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 8/2026
  96
@@ -5332,39 +5232,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 14:26:25 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 8/2026
  96
@@ -5388,39 +5288,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 13:00:45 +0200 (CEST)</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>"no.reply@wipo.int" &lt;no.reply@wipo.int&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>WIPO Account - Recovery e-mail</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>WIPO Account - Recovery e-mail
  Dear deis DEIS,
@@ -5435,39 +5335,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 13:00:45 +0200 (CEST)</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>"no.reply@wipo.int" &lt;no.reply@wipo.int&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>WIPO Account - Recovery e-mail</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>WIPO Account - Recovery e-mail
  Dear deis DEIS,
@@ -5482,39 +5382,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 21:21:59 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -5530,40 +5430,40 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 21:08:16 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -5579,39 +5479,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 21:07:44 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -5627,39 +5527,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 20:53:24 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -5673,39 +5573,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 20:39:39 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -5721,40 +5621,40 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 20:06:48 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -5770,328 +5670,40 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 4 Sep 2026 21:19:21 +0000</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>96
- Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
- Bonjour Weihai EU,
- Certaines de vos mises en vente ont été désactivées, car vos produits ne respectaient pas des exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
- Pourquoi cela se produit-il ?
- Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables. Nous nous sommes appuyés sur une combinaison de moyens automatisés et de contrôles menés par des personnes expérimentées pour identifier ce problème et prendre cette décision.
- Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
- Comment réactiver mes produits mis en vente ?
- Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
--
- Si vous disposez des documents requis, suivez les instructio</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 4 Sep 2026 21:01:23 +0000</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>96
- Presenta la documentación sobre seguridad del producto para reactivar los listings
- Hola, Weihai EU:
- Algunos de tus listings se han desactivado debido a que tus productos no cumplen los requisitos obligatorios. Revisa a continuación los detalles y siguientes pasos. Los listings afectados aparecen al final de este correo electrónico.
- ¿A qué se debe esto?
- Tomamos esta medida porque a estos productos les falta información de cumplimiento normativo obligatoria. Para más información sobre las leyes, normativas y políticas de Amazon aplicables, consulta Cumplimiento y seguridad de los productos . Hemos usado una combinación de medios automatizados y revisión humana experta para identificar la incidencia y tomar una decisión.
- En la tabla que aparece al final de este correo electrónico se proporcionan los requisitos de cumplimiento normativo específicos del producto.
- ¿Cómo puedo reactivar mis listings?
- Para proporcionar la información de cumplimiento normativo obligatoria, ve a la página Estado de la cuenta y localiza las solicitudes de cumplimiento normativo del producto:
--
- Si dispones de la documentación obligatoria, sigue las instrucciones para presentar los documentos de cum</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 4 Sep 2026 21:00:45 +0000</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>Dien productveiligheidsdocumentatie in om productvermeldingen
- opnieuw te activeren</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
- Hallo Weihai EU,
- Sommige van je productvermeldingen zijn gedeactiveerd omdat er verplichte nalevingsvereisten voor je producten ontbreken. Bekijk de gegevens en de stappen hieronder. De betreffende productvermeldingen worden aan het einde van deze e-mail weergegeven.
- Waarom gebeurt dit?
- We hebben deze actie ondernomen omdat voor deze producten verplichte nalevingsinformatie ontbreekt. Raadpleeg onze hulp-pagina Productveiligheid en -conformiteit voor informatie over de toepasselijke wet- en regelgeving en het Amazon-beleid. We hebben gebruikgemaakt van een combinatie van geautomatiseerde middelen en deskundige menselijke beoordeling om dit probleem te identificeren en deze beslissing te nemen.
- De tabel aan het einde van deze e-mail bevat productspecifieke nalevingsvereisten.
- Hoe activeer ik mijn productvermeldingen opnieuw?
- Als je de vereiste nalevingsgegevens wilt verstrekken, ga je naar de pagina Accountstatus en zoek je de aanvragen voor productconformiteit:
--
- Als je over de vereiste documentatie beschikt, volg je de instructies om je nalevingsdocumenten in te dienen. We zullen alleen </t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 4 Sep 2026 20:47:07 +0000</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
- Dzień dobry Weihai EU,
- niektóre z Twoich ofert zostały zdezaktywowane z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
- Dlaczego tak się stało?
- Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami . Do identyfikacji problemu i podjęcia decyzji wykorzystaliśmy zautomatyzowane narzędzia, a otrzymane za ich pomocą wyniki poddaliśmy weryfikacji przez eksperta.
- Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
- Jak mogę ponownie aktywować oferty?
- Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i </t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 4 Sep 2026 20:32:02 +0000</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>96
- Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
- Hej Weihai EU!
- Vissa av dina produktposter har inaktiverats på grund av att det saknas obligatorisk överensstämmelse för dina produkter. Granska informationen och följande steg nedan. De berörda produktposterna visas i slutet av det här e-postmeddelandet.
- Varför händer det här?
- Vi vidtar den här åtgärden eftersom det saknas obligatorisk information om överensstämmelse för de här produkterna. Läs vår hjälpsida för Produktsäkerhet och -överensstämmelse för information om tillämpliga lagar, förordningar och Amazons policyer. Vi har använt oss av både automatiserade metoder och mänskliga expertgranskare för att identifiera problemet och fatta det här beslutet.
- Tabellen i slutet av detta e-postmeddelande innehåller produktspecifika krav för överensstämmelse.
- Hur återaktiverar jag mina produktposter?
- Om du vill tillhandahålla den begärda överensstämmelseinformationen går du till sidan Kontostatus och letar upp begäranden om produktöverensstämmelse:
--
- Om du har den obligatoriska dokumentationen ska du skicka in dina överensstämmelsedokument enligt instruktionerna. Vi återaktiverar endast produkter som u</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 4 Sep 2026 20:04:05 +0000</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
- le offerte</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>96
- Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
- Gentile Weihai EU,
- Alcune delle tue offerte sono state disattivate a causa della mancanza di alcuni requisiti di conformità obbligatori per i tuoi prodotti. Rivedi i dettagli e i passi successivi riportati di seguito. Puoi visualizzare le offerte interessate in fondo a questa e-mail.
- Ciò a cosa è dovuto?
- Abbiamo intrapreso questo provvedimento in quanto i tuoi prodotti non dispongono delle informazioni obbligatorie sulla conformità. Consulta la pagina di aiuto Sicurezza e conformità dei prodotti per informazioni sulle leggi, le normative e le politiche di Amazon applicabili. Questa decisione è stata presa sulla base dei risultati di un'analisi effettuata in parte tramite revisione umana e in parte per mezzo di sistemi automatizzati.
- La tabella alla fine di questa e-mail contiene i requisiti di conformità specifici per i prodotti.
- Come faccio a riattivare le mie offerte?
- Per fornire le informazioni di conformità richieste, vai alla pagina Stato dell'account per individuare le richieste di conformità dei prodotti:
--
- Se disponi della documentazione richiesta, segui le istruzioni per inviare i do</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 09:37:46 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>"seller-coaching-m@amazon.com" &lt;seller-coaching-m@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13247704742] Optimize Your Next EU FBA Shipment Based on
  Inventory Health [A-AWD]</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 RE:[CASE 13247704742] Optimize Your Next EU FBA Shipment Based on Inventory Health [A-AWD]
@@ -6107,39 +5719,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 04:16:10 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-09-17</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6163,39 +5775,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 03:24:10 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6218,40 +5830,40 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 03:24:54 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Communications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>[Amazon.fr] One or More of Your Amazon Listings Have Been Search
  Suppressed</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
 [Amazon.fr] One or More of Your Amazon Listings Have Been Search Suppressed
@@ -6268,39 +5880,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 17:54:07 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (4rjrNkqMZx)</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -6320,39 +5932,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 05:00:38 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6368,39 +5980,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 10:49:16 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (j2jHyzbiUU)</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -6420,39 +6032,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 04:50:31 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6468,39 +6080,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 19:31:35 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (TrF4EN0N6o)</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -6525,39 +6137,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 15:06:42 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>"dg-seller-enrollment@amazon.com" &lt;dg-seller-enrollment@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>[Case ID:21758925371]*Your Case Resolved* You’re invited to the Dangerous Goods (Hazmat) Program US</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID:21758925371]*Your Case Resolved* You’re invited to the Dangerous Goods (Hazmat) Program US
@@ -6570,39 +6182,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 05:00:11 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6618,39 +6230,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Sun, 30 Aug 2026 14:03:08 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -6671,39 +6283,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 04:40:08 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6719,39 +6331,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 28 Aug 2026 16:34:35 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (0QNxXwzJgp)</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -6771,39 +6383,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 28 Aug 2026 15:00:25 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>"dg-seller-enrollment@amazon.com" &lt;dg-seller-enrollment@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>[Case ID:21758925371]*Your Help Needed* You’re invited to the Dangerous Goods (Hazmat) Program US</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 [Case ID:21758925371]*Your Help Needed* You’re invited to the Dangerous Goods (Hazmat) Program US
@@ -6817,39 +6429,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 28 Aug 2026 09:22:31 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6865,39 +6477,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 28 Aug 2026 04:53:03 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6913,39 +6525,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 05:02:47 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6961,39 +6573,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 23:58:41 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (0Bix9UfQE5)</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -7013,39 +6625,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 15:00:02 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>"dg-seller-enrollment@amazon.com" &lt;dg-seller-enrollment@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 21758925371] You’re invited to the Dangerous Goods (Hazmat) Program US</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 21758925371] You’re invited to the Dangerous Goods (Hazmat) Program US
@@ -7056,39 +6668,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 04:58:09 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -7104,39 +6716,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 18:49:27 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (qO7a7il03F)</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -7156,39 +6768,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 12:33:42 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (aVWN9vWwFe)</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -7208,39 +6820,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 05:00:58 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -7256,39 +6868,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Sun, 23 Aug 2026 14:55:04 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 Balance paid on your Amazon seller account
@@ -7311,39 +6923,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Sun, 23 Aug 2026 14:36:21 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 Balance paid on your Amazon seller account
@@ -7361,39 +6973,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Sun, 23 Aug 2026 04:55:13 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -7409,39 +7021,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 03:28:54 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -7457,39 +7069,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Fri, 21 Aug 2026 16:10:20 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -7510,39 +7122,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 15:24:40 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -7563,39 +7175,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 04:58:18 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -7611,39 +7223,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Wed, 19 Aug 2026 16:12:03 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -7664,39 +7276,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Tue, 18 Aug 2026 05:03:01 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -7712,39 +7324,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 04:53:18 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -7760,39 +7372,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Sun, 16 Aug 2026 04:55:15 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -7808,39 +7420,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Sun, 16 Aug 2026 02:33:51 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (TGTg3P+M9T)</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -7865,39 +7477,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -7913,39 +7525,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 04:42:49 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -7961,39 +7573,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 01:29:59 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -8014,39 +7626,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Thu, 13 Aug 2026 04:59:33 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -8062,40 +7674,40 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 15:50:39 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>A note from Katie Scott: Your spot at Amazon Accelerate 2026 is
  waiting</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-31/7z5hj9l/6869623185/h/t49nmPjAcWA0AwhOnCq47cStxvNE4bo5hge57UVyO-E)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5hj9p/6869623185/h/t49nmPjAcWA0AwhOnCq47cStxvNE4bo5hge57UVyO-E)
@@ -8109,39 +7721,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 14:51:26 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -8157,39 +7769,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 15:50:35 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -8205,39 +7817,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 15:34:38 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Three weeks out. Have you registered?</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-31/7z5hj8h/6865258013/h/R4H_C9NHvcjNXDhguSu8h5kLS8rvmJFLgxujNzlVtzg)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5hj8l/6865258013/h/R4H_C9NHvcjNXDhguSu8h5kLS8rvmJFLgxujNzlVtzg)
@@ -8251,39 +7863,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 13:47:19 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8303,39 +7915,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 13:38:54 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8352,39 +7964,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8404,39 +8016,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 10:39:58 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Envía los números de registro de RAP antes del 30 de junio</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
  You’ll be enrolled in EPR Pay on Behalf unless you provide valid Extended Producer Responsibility registration numbers by June 30
@@ -8445,39 +8057,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 10:29:17 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Early-bird pricing ends this Saturday—Register now</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-26/7z5f1dw/6858839240/h/an0hGAbEsn_GcD7m8vCy3PA0zGSpSHw1r6FwW9L-zGQ)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5f1dz/6858839240/h/an0hGAbEsn_GcD7m8vCy3PA0zGSpSHw1r6FwW9L-zGQ)
@@ -8496,39 +8108,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 00:42:21 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8545,39 +8157,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 00:41:47 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8597,39 +8209,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 10:23:35 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Final Call: Early-bird pricing ends this Saturday, 8/29—Register now</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-25/7z5dp4h/6853578557/h/fMcSGqjdqgEDoIsJN08zOUUgHxkKkP49uaYlySvIDk8)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5dp4l/6853578557/h/fMcSGqjdqgEDoIsJN08zOUUgHxkKkP49uaYlySvIDk8)
@@ -8648,39 +8260,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 12:33:59 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Sellers called this one of the highlights of Accelerate</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-24/7z5dhr3/6851676170/h/Wjp-bmbnJMm0YNVflBOldr6STH8h5YJsrXHhgAzeKUo)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5dhr6/6851676170/h/Wjp-bmbnJMm0YNVflBOldr6STH8h5YJsrXHhgAzeKUo)
@@ -8696,39 +8308,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 12:24:04 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -8752,39 +8364,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Mon, 24 Aug 2026 12:38:26 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Early-bird pricing ends August 29. Save $100 now</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-19/7z596lw/6847886297/h/fajszjfN78xb3oKGP7qMLJQXUM-VqKc8irnBicIIs-Y)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z596lz/6847886297/h/fajszjfN78xb3oKGP7qMLJQXUM-VqKc8irnBicIIs-Y)
@@ -8800,39 +8412,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 17:14:31 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8849,39 +8461,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 17:14:20 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8901,39 +8513,39 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 12:13:14 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Early-bird pricing ends Saturday, Aug. 29—Save $100 before it's full price</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-19/7z596mz/6845766770/h/4MOe7WIB0iKog9ZJ2gooAw5JI3-zJ2xmrM13S4lZjTw)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z596n3/6845766770/h/4MOe7WIB0iKog9ZJ2gooAw5JI3-zJ2xmrM13S4lZjTw)
@@ -8949,40 +8561,40 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Fri, 21 Aug 2026 10:16:19 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>The fireside chat we teased is here. Early-bird pricing ends next
  week.</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-17/7z58bwt/6843878552/h/i5ZL7d6_GwNwKOo6-EVWTgdYbnnn0rhnWQ2kP-UgsCs)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z58bwx/6843878552/h/i5ZL7d6_GwNwKOo6-EVWTgdYbnnn0rhnWQ2kP-UgsCs)
@@ -8998,39 +8610,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 16:05:40 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9050,39 +8662,39 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 16:03:47 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -9099,39 +8711,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 16:03:34 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9151,39 +8763,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 12:23:03 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>You're exactly who Accelerate was designed for</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-18/7z58zcm/6842423531/h/zqV8R_k6k7yKhqDq4dX1yXmefn5JIN40lXum5Y6M4KM)
 [Your next level starts here](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z58zcq/6842423531/h/zqV8R_k6k7yKhqDq4dX1yXmefn5JIN40lXum5Y6M4KM)
@@ -9198,40 +8810,40 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Tue, 18 Aug 2026 12:13:14 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Live at Accelerate 2026: Mary Beth Westmoreland and Amit Agarwal
  fireside chat</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-17/7z58bxx/6837257199/h/ROTGYDonH0Pvpb92J9CZAGdoz2-iazjSlqoOkDG1azg)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z58by1/6837257199/h/ROTGYDonH0Pvpb92J9CZAGdoz2-iazjSlqoOkDG1azg)
@@ -9244,39 +8856,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 18:27:13 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9293,39 +8905,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 18:26:45 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9345,39 +8957,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 13:39:43 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9397,39 +9009,39 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 13:38:59 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9446,39 +9058,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 10:11:50 +0000</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9495,39 +9107,39 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 10:11:23 +0000</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9547,39 +9159,39 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 07:03:07 +0000</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>您的亚马逊卖家账户支付的余额</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>96
 您的亚马逊卖家账户支付的余额
@@ -9608,40 +9220,40 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Thu, 13 Aug 2026 13:25:55 +0000</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Did you catch Mary Beth's message? Early-bird extension ends August
  29</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-07/7z543yq/6828853872/h/09uV_tsw5XUFTzEZF_b-1pdSpEuhEDbCowtX9OlIcwk)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z543yt/6828853872/h/09uV_tsw5XUFTzEZF_b-1pdSpEuhEDbCowtX9OlIcwk)
@@ -9655,39 +9267,139 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 4 Sep 2026 20:46:54 +0000</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 4 Sep 2026 20:32:31 +0000</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listing?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
+-
+ If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subj</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Fri, 4 Sep 2026 13:10:03 +0000</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -9704,39 +9416,39 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 20:30:25 +0000</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -9754,39 +9466,39 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 20:14:40 +0000</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -9804,39 +9516,39 @@
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 12:45:43 +0000</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr"/>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -9852,39 +9564,39 @@
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 20:11:48 +0000</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr"/>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -9902,39 +9614,39 @@
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 19:56:44 +0000</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -9952,39 +9664,39 @@
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 10:41:56 +0000</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>Submit EPR registration numbers by June 30</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>96
  You’ll be enrolled in EPR Pay on Behalf unless you provide valid Extended Producer Responsibility registration numbers by June 30
@@ -9993,39 +9705,39 @@
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 16:03:11 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>Amazon DV TIC</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr"/>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，您好。
 我们可以为您提供亚马逊DV验证报告服务。
@@ -10067,39 +9779,39 @@
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 03:08:21 +0000</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr"/>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -10118,39 +9830,39 @@
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 15:47:49 +0000</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>Seller News: August 2026</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>Seller News: August 2026
  96
@@ -10160,39 +9872,39 @@
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 08:15:11 +0000</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr"/>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -10211,39 +9923,39 @@
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 08:11:05 +0000</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr"/>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -10262,39 +9974,39 @@
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 14:08:01 +0000</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr"/>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -10312,39 +10024,39 @@
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:11:28 +0000</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr"/>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -10363,39 +10075,39 @@
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:08:21 +0000</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr"/>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -10414,39 +10126,39 @@
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:07:34 +0000</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr"/>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -10465,39 +10177,39 @@
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:07:29 +0000</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr"/>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -10516,39 +10228,39 @@
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 14:07:29 +0000</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr"/>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -10566,39 +10278,39 @@
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 13:07:04 +0000</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr"/>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -10617,39 +10329,39 @@
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 09:06:58 +0000</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr"/>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -10667,39 +10379,39 @@
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>Mon, 24 Aug 2026 16:31:11 +0000</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13205236962] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr"/>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 13205236962] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规
@@ -10734,40 +10446,40 @@
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>Mon, 24 Aug 2026 06:47:57 +0000</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr"/>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -10785,39 +10497,39 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>Sun, 23 Aug 2026 16:08:02 +0000</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr"/>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -10835,39 +10547,39 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 23:14:29 +0000</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr"/>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -10885,39 +10597,39 @@
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 12:34:53 +0000</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr"/>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -10933,39 +10645,39 @@
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>Fri, 21 Aug 2026 23:11:47 +0000</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr"/>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -10983,39 +10695,39 @@
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>Tue, 18 Aug 2026 10:06:05 +0000</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr"/>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -11042,39 +10754,39 @@
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>Thu, 13 Aug 2026 16:08:49 +0000</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr"/>
-      <c r="H208" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -11092,39 +10804,39 @@
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>Thu, 13 Aug 2026 04:08:25 +0000</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr"/>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -11142,39 +10854,39 @@
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>Wed, 12 Aug 2026 16:13:04 +0000</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>Update tax information to prepare for UAE e-invoicing requirements</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr"/>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>96
  Update tax information to prepare for UAE e-invoicing requirements
@@ -11186,6 +10898,294 @@
 - Ensure your Trade License, Emirates ID, and Passport number are valid in Identity Information .
 - Confirm your legal name in Identity Information matches your Federal Tax Authority records exactly. If your information is incomplete or incorrect, your ability to claim VAT on our invoices may be impacted.
  If your business is subject to UAE e-invoicing requirements, you must register at a Federal Tax Authority-accredited UAE Peppol Access Point according to your implementation phase. This enables the exchange of e-invoices through the UAE e-invoicing network. You'll also need to issue compliant e-in</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 4 Sep 2026 21:19:21 +0000</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
+ Bonjour Weihai EU,
+ Certaines de vos mises en vente ont été désactivées, car vos produits ne respectaient pas des exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
+ Pourquoi cela se produit-il ?
+ Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables. Nous nous sommes appuyés sur une combinaison de moyens automatisés et de contrôles menés par des personnes expérimentées pour identifier ce problème et prendre cette décision.
+ Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
+ Comment réactiver mes produits mis en vente ?
+ Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
+-
+ Si vous disposez des documents requis, suivez les instructio</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 4 Sep 2026 21:01:23 +0000</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Presenta la documentación sobre seguridad del producto para reactivar los listings
+ Hola, Weihai EU:
+ Algunos de tus listings se han desactivado debido a que tus productos no cumplen los requisitos obligatorios. Revisa a continuación los detalles y siguientes pasos. Los listings afectados aparecen al final de este correo electrónico.
+ ¿A qué se debe esto?
+ Tomamos esta medida porque a estos productos les falta información de cumplimiento normativo obligatoria. Para más información sobre las leyes, normativas y políticas de Amazon aplicables, consulta Cumplimiento y seguridad de los productos . Hemos usado una combinación de medios automatizados y revisión humana experta para identificar la incidencia y tomar una decisión.
+ En la tabla que aparece al final de este correo electrónico se proporcionan los requisitos de cumplimiento normativo específicos del producto.
+ ¿Cómo puedo reactivar mis listings?
+ Para proporcionar la información de cumplimiento normativo obligatoria, ve a la página Estado de la cuenta y localiza las solicitudes de cumplimiento normativo del producto:
+-
+ Si dispones de la documentación obligatoria, sigue las instrucciones para presentar los documentos de cum</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 4 Sep 2026 21:00:45 +0000</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>Dien productveiligheidsdocumentatie in om productvermeldingen
+ opnieuw te activeren</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
+ Hallo Weihai EU,
+ Sommige van je productvermeldingen zijn gedeactiveerd omdat er verplichte nalevingsvereisten voor je producten ontbreken. Bekijk de gegevens en de stappen hieronder. De betreffende productvermeldingen worden aan het einde van deze e-mail weergegeven.
+ Waarom gebeurt dit?
+ We hebben deze actie ondernomen omdat voor deze producten verplichte nalevingsinformatie ontbreekt. Raadpleeg onze hulp-pagina Productveiligheid en -conformiteit voor informatie over de toepasselijke wet- en regelgeving en het Amazon-beleid. We hebben gebruikgemaakt van een combinatie van geautomatiseerde middelen en deskundige menselijke beoordeling om dit probleem te identificeren en deze beslissing te nemen.
+ De tabel aan het einde van deze e-mail bevat productspecifieke nalevingsvereisten.
+ Hoe activeer ik mijn productvermeldingen opnieuw?
+ Als je de vereiste nalevingsgegevens wilt verstrekken, ga je naar de pagina Accountstatus en zoek je de aanvragen voor productconformiteit:
+-
+ Als je over de vereiste documentatie beschikt, volg je de instructies om je nalevingsdocumenten in te dienen. We zullen alleen </t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 4 Sep 2026 20:47:07 +0000</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
+ Dzień dobry Weihai EU,
+ niektóre z Twoich ofert zostały zdezaktywowane z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
+ Dlaczego tak się stało?
+ Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami . Do identyfikacji problemu i podjęcia decyzji wykorzystaliśmy zautomatyzowane narzędzia, a otrzymane za ich pomocą wyniki poddaliśmy weryfikacji przez eksperta.
+ Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
+ Jak mogę ponownie aktywować oferty?
+ Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i </t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 4 Sep 2026 20:32:02 +0000</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
+ Hej Weihai EU!
+ Vissa av dina produktposter har inaktiverats på grund av att det saknas obligatorisk överensstämmelse för dina produkter. Granska informationen och följande steg nedan. De berörda produktposterna visas i slutet av det här e-postmeddelandet.
+ Varför händer det här?
+ Vi vidtar den här åtgärden eftersom det saknas obligatorisk information om överensstämmelse för de här produkterna. Läs vår hjälpsida för Produktsäkerhet och -överensstämmelse för information om tillämpliga lagar, förordningar och Amazons policyer. Vi har använt oss av både automatiserade metoder och mänskliga expertgranskare för att identifiera problemet och fatta det här beslutet.
+ Tabellen i slutet av detta e-postmeddelande innehåller produktspecifika krav för överensstämmelse.
+ Hur återaktiverar jag mina produktposter?
+ Om du vill tillhandahålla den begärda överensstämmelseinformationen går du till sidan Kontostatus och letar upp begäranden om produktöverensstämmelse:
+-
+ Om du har den obligatoriska dokumentationen ska du skicka in dina överensstämmelsedokument enligt instruktionerna. Vi återaktiverar endast produkter som u</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 4 Sep 2026 20:04:05 +0000</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
+ le offerte</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
+ Gentile Weihai EU,
+ Alcune delle tue offerte sono state disattivate a causa della mancanza di alcuni requisiti di conformità obbligatori per i tuoi prodotti. Rivedi i dettagli e i passi successivi riportati di seguito. Puoi visualizzare le offerte interessate in fondo a questa e-mail.
+ Ciò a cosa è dovuto?
+ Abbiamo intrapreso questo provvedimento in quanto i tuoi prodotti non dispongono delle informazioni obbligatorie sulla conformità. Consulta la pagina di aiuto Sicurezza e conformità dei prodotti per informazioni sulle leggi, le normative e le politiche di Amazon applicabili. Questa decisione è stata presa sulla base dei risultati di un'analisi effettuata in parte tramite revisione umana e in parte per mezzo di sistemi automatizzati.
+ La tabella alla fine di questa e-mail contiene i requisiti di conformità specifici per i prodotti.
+ Come faccio a riattivare le mie offerte?
+ Per fornire le informazioni di conformità richieste, vai alla pagina Stato dell'account per individuare le richieste di conformità dei prodotti:
+-
+ Se disponi della documentazione richiesta, segui le istruzioni per inviare i do</t>
         </is>
       </c>
     </row>
